--- a/artfynd/A 25029-2022 artfynd.xlsx
+++ b/artfynd/A 25029-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25029-2022 artfynd.xlsx
+++ b/artfynd/A 25029-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101679808</v>
+        <v>101679809</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446557.5133811287</v>
+        <v>446723</v>
       </c>
       <c r="R2" t="n">
-        <v>7053747.391226459</v>
+        <v>7053735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2022-06-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +758,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,57 +776,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102970944</v>
+        <v>101679810</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kävåsen, Fiskviken, Offerdal, Jmt</t>
+          <t>Hammarhön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446757.2953349221</v>
+        <v>447064</v>
       </c>
       <c r="R3" t="n">
-        <v>7054074.665023177</v>
+        <v>7053795</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,80 +859,70 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102970964</v>
+        <v>101679808</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kävåsen, Fiskviken, Offerdal, Jmt</t>
+          <t>Hammarhön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447025.4007109989</v>
+        <v>446557</v>
       </c>
       <c r="R4" t="n">
-        <v>7054147.154972704</v>
+        <v>7053748</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +946,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,137 +960,22 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>102970910</v>
-      </c>
-      <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Kävåsen, Fiskviken, Offerdal, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>446984.0410004756</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7054098.454776103</v>
-      </c>
-      <c r="S5" t="n">
-        <v>75</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25029-2022 artfynd.xlsx
+++ b/artfynd/A 25029-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101679809</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101679810</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,8 +991,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101679808</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>